--- a/artfynd/A 39468-2026 artfynd.xlsx
+++ b/artfynd/A 39468-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137226359</v>
       </c>
       <c r="B3" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137226368</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137226376</v>
       </c>
       <c r="B5" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>137226375</v>
       </c>
       <c r="B6" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137226374</v>
       </c>
       <c r="B13" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 39468-2026 artfynd.xlsx
+++ b/artfynd/A 39468-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137226371</v>
       </c>
       <c r="B2" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137226359</v>
       </c>
       <c r="B3" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137226368</v>
       </c>
       <c r="B4" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137226376</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>137226375</v>
       </c>
       <c r="B6" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>137226364</v>
       </c>
       <c r="B7" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>137226370</v>
       </c>
       <c r="B8" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137226360</v>
       </c>
       <c r="B9" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137226363</v>
       </c>
       <c r="B10" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>137226373</v>
       </c>
       <c r="B11" t="n">
-        <v>80623</v>
+        <v>80633</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>137226362</v>
       </c>
       <c r="B12" t="n">
-        <v>78503</v>
+        <v>78513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137226374</v>
       </c>
       <c r="B13" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>137226369</v>
       </c>
       <c r="B14" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>137226372</v>
       </c>
       <c r="B15" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39468-2026 artfynd.xlsx
+++ b/artfynd/A 39468-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137226359</v>
       </c>
       <c r="B3" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137226368</v>
       </c>
       <c r="B4" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137226376</v>
       </c>
       <c r="B5" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>137226375</v>
       </c>
       <c r="B6" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137226374</v>
       </c>
       <c r="B13" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 39468-2026 artfynd.xlsx
+++ b/artfynd/A 39468-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137226371</v>
       </c>
       <c r="B2" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137226359</v>
       </c>
       <c r="B3" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137226368</v>
       </c>
       <c r="B4" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137226376</v>
       </c>
       <c r="B5" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>137226375</v>
       </c>
       <c r="B6" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
         <v>137226364</v>
       </c>
       <c r="B7" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>137226370</v>
       </c>
       <c r="B8" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137226360</v>
       </c>
       <c r="B9" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>137226363</v>
       </c>
       <c r="B10" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>137226373</v>
       </c>
       <c r="B11" t="n">
-        <v>80633</v>
+        <v>80636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>137226362</v>
       </c>
       <c r="B12" t="n">
-        <v>78513</v>
+        <v>78516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137226374</v>
       </c>
       <c r="B13" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>137226369</v>
       </c>
       <c r="B14" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>137226372</v>
       </c>
       <c r="B15" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 39468-2026 artfynd.xlsx
+++ b/artfynd/A 39468-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137226359</v>
       </c>
       <c r="B3" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137226368</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>137226376</v>
       </c>
       <c r="B5" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>137226375</v>
       </c>
       <c r="B6" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>137226374</v>
       </c>
       <c r="B13" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 39468-2026 artfynd.xlsx
+++ b/artfynd/A 39468-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137226371</v>
       </c>
       <c r="B2" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137226359</v>
       </c>
       <c r="B3" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137226368</v>
+        <v>137404029</v>
       </c>
       <c r="B4" t="n">
-        <v>93463</v>
+        <v>91173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,37 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Klockstaplarna, Älvsbyn, Nb</t>
+          <t>Klockstaplarna, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>774586</v>
+        <v>774609</v>
       </c>
       <c r="R4" t="n">
-        <v>7291486</v>
+        <v>7291685</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,45 +960,54 @@
           <t>2026-10-11</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137226368</t>
+          <t>https://artportalen.se/Sighting/137404029</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137226376</v>
+        <v>137226368</v>
       </c>
       <c r="B5" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>774513</v>
+        <v>774586</v>
       </c>
       <c r="R5" t="n">
-        <v>7291609</v>
+        <v>7291486</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,16 +1104,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137226376</t>
+          <t>https://artportalen.se/Sighting/137226368</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137226375</v>
+        <v>137226376</v>
       </c>
       <c r="B6" t="n">
-        <v>93501</v>
+        <v>93469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,33 +1121,25 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1150,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>774501</v>
+        <v>774513</v>
       </c>
       <c r="R6" t="n">
-        <v>7291588</v>
+        <v>7291609</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1212,16 +1210,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137226375</t>
+          <t>https://artportalen.se/Sighting/137226376</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137226364</v>
+        <v>137404041</v>
       </c>
       <c r="B7" t="n">
-        <v>78919</v>
+        <v>93112</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1229,37 +1227,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>4745</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Klockstaplarna, Älvsbyn, Nb</t>
+          <t>Klockstaplarna, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>774632</v>
+        <v>774472</v>
       </c>
       <c r="R7" t="n">
-        <v>7291642</v>
+        <v>7291588</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1289,45 +1284,54 @@
           <t>2026-10-11</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137226364</t>
+          <t>https://artportalen.se/Sighting/137404041</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137226370</v>
+        <v>137226375</v>
       </c>
       <c r="B8" t="n">
-        <v>79273</v>
+        <v>93507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,25 +1339,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1362,13 +1374,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>774563</v>
+        <v>774501</v>
       </c>
       <c r="R8" t="n">
-        <v>7291442</v>
+        <v>7291588</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,16 +1436,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137226370</t>
+          <t>https://artportalen.se/Sighting/137226375</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137226360</v>
+        <v>137404031</v>
       </c>
       <c r="B9" t="n">
-        <v>80135</v>
+        <v>93507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1441,40 +1453,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Klockstaplarna, Älvsbyn, Nb</t>
+          <t>Klockstaplarna, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>774617</v>
+        <v>774612</v>
       </c>
       <c r="R9" t="n">
-        <v>7291703</v>
+        <v>7291590</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1501,45 +1510,54 @@
           <t>2026-10-11</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137226360</t>
+          <t>https://artportalen.se/Sighting/137404031</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137226363</v>
+        <v>137404040</v>
       </c>
       <c r="B10" t="n">
-        <v>80135</v>
+        <v>93507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1547,40 +1565,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Klockstaplarna, Älvsbyn, Nb</t>
+          <t>Klockstaplarna, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>774625</v>
+        <v>774489</v>
       </c>
       <c r="R10" t="n">
-        <v>7291642</v>
+        <v>7291602</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1607,83 +1622,89 @@
           <t>2026-10-11</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137226363</t>
+          <t>https://artportalen.se/Sighting/137404040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137226373</v>
+        <v>137404036</v>
       </c>
       <c r="B11" t="n">
-        <v>80636</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Klockstaplarna, Älvsbyn, Nb</t>
+          <t>Klockstaplarna, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>774471</v>
+        <v>774531</v>
       </c>
       <c r="R11" t="n">
-        <v>7291536</v>
+        <v>7291443</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1713,45 +1734,54 @@
           <t>2026-10-11</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137226373</t>
+          <t>https://artportalen.se/Sighting/137404036</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137226362</v>
+        <v>137226364</v>
       </c>
       <c r="B12" t="n">
-        <v>78516</v>
+        <v>78924</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1759,21 +1789,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1786,7 +1816,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>774625</v>
+        <v>774632</v>
       </c>
       <c r="R12" t="n">
         <v>7291642</v>
@@ -1848,58 +1878,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137226362</t>
+          <t>https://artportalen.se/Sighting/137226364</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137226374</v>
+        <v>137404033</v>
       </c>
       <c r="B13" t="n">
-        <v>99412</v>
+        <v>78924</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Klockstaplarna, Älvsbyn, Nb</t>
+          <t>Klockstaplarna, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>774485</v>
+        <v>774621</v>
       </c>
       <c r="R13" t="n">
-        <v>7291566</v>
+        <v>7291598</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1926,45 +1952,54 @@
           <t>2026-10-11</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137226374</t>
+          <t>https://artportalen.se/Sighting/137404033</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137226369</v>
+        <v>137226370</v>
       </c>
       <c r="B14" t="n">
-        <v>79274</v>
+        <v>79278</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1972,21 +2007,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2061,16 +2096,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137226369</t>
+          <t>https://artportalen.se/Sighting/137226370</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137226372</v>
+        <v>137226360</v>
       </c>
       <c r="B15" t="n">
-        <v>79274</v>
+        <v>80140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2078,21 +2113,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2105,13 +2140,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>774499</v>
+        <v>774617</v>
       </c>
       <c r="R15" t="n">
-        <v>7291455</v>
+        <v>7291703</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2167,7 +2202,1430 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137226360</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137226363</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80140</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Klockstaplarna, Älvsbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>774625</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7291642</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137226363</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137404038</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80530</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Klockstaplarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>774470</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7291534</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404038</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137226373</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80641</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Klockstaplarna, Älvsbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>774471</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7291536</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137226373</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137226362</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78521</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Klockstaplarna, Älvsbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>774625</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7291642</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137226362</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137404032</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78521</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Klockstaplarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>774622</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7291601</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404032</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137404028</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57221</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Klockstaplarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>774575</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7291736</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404028</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137404027</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58196</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Klockstaplarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>774556</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7291753</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404027</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137226374</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99418</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Klockstaplarna, Älvsbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>774485</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7291566</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137226374</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137404039</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99418</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Klockstaplarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>774477</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7291547</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404039</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137404044</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98280</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Klockstaplarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>774507</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7291667</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404044</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137226369</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79279</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Klockstaplarna, Älvsbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>774563</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7291442</v>
+      </c>
+      <c r="S26" t="n">
+        <v>6</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137226369</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137226372</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79279</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Klockstaplarna, Älvsbyn, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>774499</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7291455</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137226372</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137404045</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79544</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Klockstaplarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>774490</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7291707</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137404045</t>
         </is>
       </c>
     </row>
@@ -2187,6 +3645,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39468-2026 artfynd.xlsx
+++ b/artfynd/A 39468-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137226371</v>
       </c>
       <c r="B2" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137226359</v>
       </c>
       <c r="B3" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137404029</v>
       </c>
       <c r="B4" t="n">
-        <v>91173</v>
+        <v>91185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>137226368</v>
       </c>
       <c r="B5" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>137226376</v>
       </c>
       <c r="B6" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137404041</v>
       </c>
       <c r="B7" t="n">
-        <v>93112</v>
+        <v>93124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137226375</v>
       </c>
       <c r="B8" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>137404031</v>
       </c>
       <c r="B9" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>137404040</v>
       </c>
       <c r="B10" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>137404036</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>137226364</v>
       </c>
       <c r="B12" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>137404033</v>
       </c>
       <c r="B13" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>137226370</v>
       </c>
       <c r="B14" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>137226360</v>
       </c>
       <c r="B15" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>137226363</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>137404038</v>
       </c>
       <c r="B17" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>137226373</v>
       </c>
       <c r="B18" t="n">
-        <v>80641</v>
+        <v>80652</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>137226362</v>
       </c>
       <c r="B19" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>137404032</v>
       </c>
       <c r="B20" t="n">
-        <v>78521</v>
+        <v>78532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>137226374</v>
       </c>
       <c r="B23" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>137404039</v>
       </c>
       <c r="B24" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>137404044</v>
       </c>
       <c r="B25" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>137226369</v>
       </c>
       <c r="B26" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>137226372</v>
       </c>
       <c r="B27" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>137404045</v>
       </c>
       <c r="B28" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 39468-2026 artfynd.xlsx
+++ b/artfynd/A 39468-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137226371</v>
       </c>
       <c r="B2" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137226359</v>
       </c>
       <c r="B3" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137404029</v>
       </c>
       <c r="B4" t="n">
-        <v>91185</v>
+        <v>91186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>137226368</v>
       </c>
       <c r="B5" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>137226376</v>
       </c>
       <c r="B6" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137404041</v>
       </c>
       <c r="B7" t="n">
-        <v>93124</v>
+        <v>93125</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137226375</v>
       </c>
       <c r="B8" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>137404031</v>
       </c>
       <c r="B9" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>137404040</v>
       </c>
       <c r="B10" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>137404036</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>137226364</v>
       </c>
       <c r="B12" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>137404033</v>
       </c>
       <c r="B13" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>137226370</v>
       </c>
       <c r="B14" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>137226360</v>
       </c>
       <c r="B15" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>137226363</v>
       </c>
       <c r="B16" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>137404038</v>
       </c>
       <c r="B17" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>137226373</v>
       </c>
       <c r="B18" t="n">
-        <v>80652</v>
+        <v>80653</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>137226362</v>
       </c>
       <c r="B19" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>137404032</v>
       </c>
       <c r="B20" t="n">
-        <v>78532</v>
+        <v>78533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>137226374</v>
       </c>
       <c r="B23" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>137404039</v>
       </c>
       <c r="B24" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>137404044</v>
       </c>
       <c r="B25" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>137226369</v>
       </c>
       <c r="B26" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>137226372</v>
       </c>
       <c r="B27" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>137404045</v>
       </c>
       <c r="B28" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 39468-2026 artfynd.xlsx
+++ b/artfynd/A 39468-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137226371</v>
       </c>
       <c r="B2" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137226359</v>
       </c>
       <c r="B3" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137404029</v>
       </c>
       <c r="B4" t="n">
-        <v>91186</v>
+        <v>91189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>137226368</v>
       </c>
       <c r="B5" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>137226376</v>
       </c>
       <c r="B6" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137404041</v>
       </c>
       <c r="B7" t="n">
-        <v>93125</v>
+        <v>93128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137226375</v>
       </c>
       <c r="B8" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>137404031</v>
       </c>
       <c r="B9" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>137404040</v>
       </c>
       <c r="B10" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>137404036</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>137226364</v>
       </c>
       <c r="B12" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>137404033</v>
       </c>
       <c r="B13" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>137226370</v>
       </c>
       <c r="B14" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>137226360</v>
       </c>
       <c r="B15" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>137226363</v>
       </c>
       <c r="B16" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>137404038</v>
       </c>
       <c r="B17" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>137226373</v>
       </c>
       <c r="B18" t="n">
-        <v>80653</v>
+        <v>80655</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>137226362</v>
       </c>
       <c r="B19" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>137404032</v>
       </c>
       <c r="B20" t="n">
-        <v>78533</v>
+        <v>78535</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>137226374</v>
       </c>
       <c r="B23" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>137404039</v>
       </c>
       <c r="B24" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>137404044</v>
       </c>
       <c r="B25" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>137226369</v>
       </c>
       <c r="B26" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>137226372</v>
       </c>
       <c r="B27" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>137404045</v>
       </c>
       <c r="B28" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 39468-2026 artfynd.xlsx
+++ b/artfynd/A 39468-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137226371</v>
       </c>
       <c r="B2" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>137226359</v>
       </c>
       <c r="B3" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>137404029</v>
       </c>
       <c r="B4" t="n">
-        <v>91189</v>
+        <v>91193</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>137226368</v>
       </c>
       <c r="B5" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>137226376</v>
       </c>
       <c r="B6" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137404041</v>
       </c>
       <c r="B7" t="n">
-        <v>93128</v>
+        <v>93132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137226375</v>
       </c>
       <c r="B8" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>137404031</v>
       </c>
       <c r="B9" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>137404040</v>
       </c>
       <c r="B10" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>137404036</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>137226364</v>
       </c>
       <c r="B12" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>137404033</v>
       </c>
       <c r="B13" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>137226370</v>
       </c>
       <c r="B14" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>137226360</v>
       </c>
       <c r="B15" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>137226363</v>
       </c>
       <c r="B16" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>137404038</v>
       </c>
       <c r="B17" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>137226373</v>
       </c>
       <c r="B18" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>137226362</v>
       </c>
       <c r="B19" t="n">
-        <v>78535</v>
+        <v>78539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>137404032</v>
       </c>
       <c r="B20" t="n">
-        <v>78535</v>
+        <v>78539</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>137404028</v>
       </c>
       <c r="B21" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>137404027</v>
       </c>
       <c r="B22" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>137226374</v>
       </c>
       <c r="B23" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>137404039</v>
       </c>
       <c r="B24" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>137404044</v>
       </c>
       <c r="B25" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>137226369</v>
       </c>
       <c r="B26" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>137226372</v>
       </c>
       <c r="B27" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
         <v>137404045</v>
       </c>
       <c r="B28" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
